--- a/public/records.xlsx
+++ b/public/records.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Все" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Женщины, бассейн 50 м" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Женщины, бассейн 25 м" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мужчины, бассейн 50 м" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мужчины, бассейн 25 м" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Смешанные эстафеты" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Все" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Женщины, бассейн 50 м" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Женщины, бассейн 25 м" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Мужчины, бассейн 50 м" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Мужчины, бассейн 25 м" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Смешанные эстафеты" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +32,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00FAFAFA"/>
     </font>
     <font>
       <name val="Menlo"/>
@@ -47,7 +47,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000369A1"/>
+        <fgColor rgb="000D0D0D"/>
       </patternFill>
     </fill>
   </fills>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J91"/>
+  <dimension ref="A1:J92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -519,7 +519,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Фесикова Анастасия</t>
+          <t>Гайфутдинова Алина</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -535,17 +535,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Глазго</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>04.08.2018</t>
+          <t>19.04.2026</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2018-08-04</t>
+          <t>2026-04-19</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>брасс 50 м</t>
+          <t>на спине 50 м</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -567,33 +567,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ефимова Юлия</t>
+          <t>Фесикова Анастасия</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>27.23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>27.23</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Барселона</t>
+          <t>Глазго</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>04.08.2013</t>
+          <t>04.08.2018</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2013-08-04</t>
+          <t>2018-08-04</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>баттерфляй 50 м</t>
+          <t>брасс 50 м</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -615,33 +615,33 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Суркова Арина</t>
+          <t>Ефимова Юлия</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Барселона</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>19.04.2023</t>
+          <t>04.08.2013</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2013-08-04</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>вольный стиль 50 м</t>
+          <t>баттерфляй 50 м</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -663,18 +663,18 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Каменева Мария</t>
+          <t>Суркова Арина</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24.20</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>24.20</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -684,12 +684,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>09.04.2021</t>
+          <t>19.04.2023</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2021-04-09</t>
+          <t>2023-04-19</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>на спине 100 м</t>
+          <t>вольный стиль 50 м</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -711,33 +711,33 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Зуева Анастасия</t>
+          <t>Каменева Мария</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>58.18</t>
+          <t>24.20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>58.18</t>
+          <t>24.20</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Рим</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>28.07.2009</t>
+          <t>09.04.2021</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2009-07-28</t>
+          <t>2021-04-09</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>брасс 100 м</t>
+          <t>на спине 100 м</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -759,33 +759,33 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ефимова Юлия</t>
+          <t>Зуева Анастасия</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1:04.36</t>
+          <t>58.18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>64.36</t>
+          <t>58.18</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Рим</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>24.07.2017</t>
+          <t>28.07.2009</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2017-07-24</t>
+          <t>2009-07-28</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>баттерфляй 100 м</t>
+          <t>брасс 100 м</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -807,33 +807,33 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Клепикова Дарья</t>
+          <t>Ефимова Юлия</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>56.42</t>
+          <t>1:04.36</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>56.42</t>
+          <t>64.36</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Сингапур</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>27.07.2025</t>
+          <t>24.07.2017</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2017-07-24</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>вольный стиль 100 м</t>
+          <t>баттерфляй 100 м</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -861,12 +861,12 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>52.98</t>
+          <t>56.42</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>52.98</t>
+          <t>56.42</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>01.08.2025</t>
+          <t>27.07.2025</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-07-27</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>на спине 200 м</t>
+          <t>вольный стиль 100 м</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -903,33 +903,33 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Зуева Анастасия</t>
+          <t>Клепикова Дарья</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2:04.94</t>
+          <t>52.98</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>124.94</t>
+          <t>52.98</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Рим</t>
+          <t>Сингапур</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>01.08.2009</t>
+          <t>01.08.2025</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>брасс 200 м</t>
+          <t>на спине 200 м</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -951,33 +951,33 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Чикунова Евгения</t>
+          <t>Зуева Анастасия</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2:17.55</t>
+          <t>2:04.94</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>137.55</t>
+          <t>124.94</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Рим</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>21.04.2023</t>
+          <t>01.08.2009</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2023-04-21</t>
+          <t>2009-08-01</t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>баттерфляй 200 м</t>
+          <t>брасс 200 м</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -999,33 +999,33 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Чимрова Светлана</t>
+          <t>Чикунова Евгения</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2:07.33</t>
+          <t>2:17.55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>127.33</t>
+          <t>137.55</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Глазго</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>06.08.2018</t>
+          <t>21.04.2023</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2018-08-06</t>
+          <t>2023-04-21</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>вольный стиль 200 м</t>
+          <t>баттерфляй 200 м</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1047,33 +1047,33 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Попова Вероника</t>
+          <t>Чимрова Светлана</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1:55.08</t>
+          <t>2:07.33</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>115.08</t>
+          <t>127.33</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Глазго</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25.07.2017</t>
+          <t>06.08.2018</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2017-07-25</t>
+          <t>2018-08-06</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>комплексное плавание 200 м</t>
+          <t>вольный стиль 200 м</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1095,33 +1095,33 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Андреева Виктория</t>
+          <t>Попова Вероника</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2:09.56</t>
+          <t>1:55.08</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>129.56</t>
+          <t>115.08</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>19.04.2016</t>
+          <t>25.07.2017</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2016-04-19</t>
+          <t>2017-07-25</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>вольный стиль 400 м</t>
+          <t>комплексное плавание 200 м</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1143,33 +1143,33 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Егорова Анна</t>
+          <t>Андреева Виктория</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4:04.10</t>
+          <t>2:09.56</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>244.10</t>
+          <t>129.56</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>04.04.2021</t>
+          <t>19.04.2016</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2021-04-04</t>
+          <t>2016-04-19</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>комплексное плавание 400 м</t>
+          <t>вольный стиль 400 м</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1191,33 +1191,33 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Мартынова Яна</t>
+          <t>Егорова Анна</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>4:36.25</t>
+          <t>4:04.10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>276.25</t>
+          <t>244.10</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Пекин</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>09.08.2008</t>
+          <t>04.04.2021</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2008-08-09</t>
+          <t>2021-04-04</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>вольный стиль 800 м</t>
+          <t>комплексное плавание 400 м</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1239,33 +1239,33 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Кирпичникова Анастасия</t>
+          <t>Мартынова Яна</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>8:18.77</t>
+          <t>4:36.25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>498.77</t>
+          <t>276.25</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Токио</t>
+          <t>Пекин</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>29.07.2021</t>
+          <t>09.08.2008</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2021-07-29</t>
+          <t>2008-08-09</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>вольный стиль 1500 м</t>
+          <t>вольный стиль 800 м</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1293,12 +1293,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>15:50.22</t>
+          <t>8:18.77</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>950.22</t>
+          <t>498.77</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>26.07.2021</t>
+          <t>29.07.2021</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2021-07-26</t>
+          <t>2021-07-29</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,43 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4 х 100 м вольный стиль</t>
+          <t>вольный стиль 1500 м</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>эстафета</t>
+          <t>личное</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Сборная России</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Трофимова Дарья · Кузнецова Александра · Гайфутдинова Алина · Клепикова Дарья</t>
-        </is>
-      </c>
+          <t>Кирпичникова Анастасия</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3:34.69</t>
+          <t>15:50.22</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>214.69</t>
+          <t>950.22</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Сингапур</t>
+          <t>Токио</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>27.07.2025</t>
+          <t>26.07.2021</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2021-07-26</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1373,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4 х 100 м комбинированная</t>
+          <t>4 х 100 м вольный стиль</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1392,32 +1388,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Фесикова Анастасия · Ефимова Юлия · Чимрова Светлана · Попова Вероника</t>
+          <t>Трофимова Дарья · Кузнецова Александра · Гайфутдинова Алина · Клепикова Дарья</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>3:53.38</t>
+          <t>3:34.69</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>233.38</t>
+          <t>214.69</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Сингапур</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30.07.2017</t>
+          <t>27.07.2025</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2017-07-30</t>
+          <t>2025-07-27</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1425,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4 х 200 м вольный стиль</t>
+          <t>4 х 100 м комбинированная</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1444,80 +1440,84 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Егорова Анна · Гуженкова Анастасия · Саламатина Валерия · Андрусенко Вероника</t>
+          <t>Фесикова Анастасия · Ефимова Юлия · Чимрова Светлана · Попова Вероника</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>7:48.25</t>
+          <t>3:53.38</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>468.25</t>
+          <t>233.38</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Кванджу</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>25.07.2019</t>
+          <t>30.07.2017</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2019-07-25</t>
+          <t>2017-07-30</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Женщины, бассейн 25 м</t>
+          <t>Женщины, бассейн 50 м</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>на спине 50 м (бассейн 25 м)</t>
+          <t>4 х 200 м вольный стиль</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>личное</t>
+          <t>эстафета</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Каменева Мария</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>Сборная России</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Егорова Анна · Гуженкова Анастасия · Саламатина Валерия · Андрусенко Вероника</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25.60</t>
+          <t>7:48.25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>25.60</t>
+          <t>468.25</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Кванджу</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>24.11.2022</t>
+          <t>25.07.2019</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2022-11-24</t>
+          <t>2019-07-25</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>брасс 50 м  (бассейн 25 м)</t>
+          <t>на спине 50 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1539,33 +1539,33 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ефимова Юлия</t>
+          <t>Каменева Мария</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>25.60</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>25.60</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Берлин</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>21.10.2013</t>
+          <t>24.11.2022</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2013-10-21</t>
+          <t>2022-11-24</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>баттерфляй 50 м (бассейн 25 м)</t>
+          <t>брасс 50 м  (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1587,33 +1587,33 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Суркова Арина</t>
+          <t>Ефимова Юлия</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>24.58</t>
+          <t>29.08</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>24.58</t>
+          <t>29.08</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Санкт-Петербург</t>
+          <t>Берлин</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>22.11.2023</t>
+          <t>21.10.2013</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2023-11-22</t>
+          <t>2013-10-21</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>вольный стиль 50 м (бассейн 25 м)</t>
+          <t>баттерфляй 50 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1635,18 +1635,18 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Каменева Мария</t>
+          <t>Суркова Арина</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>23.34</t>
+          <t>24.58</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>23.34</t>
+          <t>24.58</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>16.12.2022</t>
+          <t>22.11.2023</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2022-12-16</t>
+          <t>2023-11-22</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>на спине 100 м (бассейн 25 м)</t>
+          <t>вольный стиль 50 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1689,12 +1689,12 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>55.83</t>
+          <t>23.34</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>55.83</t>
+          <t>23.34</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>18.12.2022</t>
+          <t>16.12.2022</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-12-16</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>брасс 100 м (бассейн 25 м)</t>
+          <t>на спине 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1731,33 +1731,33 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ефимова Юлия</t>
+          <t>Каменева Мария</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1:02.91</t>
+          <t>55.83</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>62.91</t>
+          <t>55.83</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>03.09.2016</t>
+          <t>18.12.2022</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2016-09-03</t>
+          <t>2022-12-18</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>баттерфляй 100 м (бассейн 25 м)</t>
+          <t>брасс 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1779,33 +1779,33 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Суркова Арина</t>
+          <t>Ефимова Юлия</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>55.63</t>
+          <t>1:02.91</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>55.63</t>
+          <t>62.91</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Санкт-Петербург</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>25.11.2023</t>
+          <t>03.09.2016</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2016-09-03</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>вольный стиль 100 м (бассейн 25 м)</t>
+          <t>баттерфляй 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1827,33 +1827,33 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Клепикова Дарья</t>
+          <t>Суркова Арина</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>51.62</t>
+          <t>55.63</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>51.62</t>
+          <t>55.63</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>12.12.2024</t>
+          <t>25.11.2023</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2023-11-25</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>комплексное плавание 100 м (бассейн 25 м)</t>
+          <t>вольный стиль 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1875,33 +1875,33 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Каменева Мария</t>
+          <t>Клепикова Дарья</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>57.59</t>
+          <t>51.62</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>57.59</t>
+          <t>51.62</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Глазго</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>06.12.2019</t>
+          <t>12.12.2024</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2019-12-06</t>
+          <t>2024-12-12</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>на спине 200 м (бассейн 25 м)</t>
+          <t>комплексное плавание 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1923,33 +1923,33 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Устинова Дарья К.</t>
+          <t>Каменева Мария</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2:01.57</t>
+          <t>57.59</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>121.57</t>
+          <t>57.59</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Нетания</t>
+          <t>Глазго</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>04.12.2015</t>
+          <t>06.12.2019</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2015-12-04</t>
+          <t>2019-12-06</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>брасс 200 м (бассейн 25 м)</t>
+          <t>на спине 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1971,33 +1971,33 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Чикунова Евгения</t>
+          <t>Устинова Дарья К.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2:14.70</t>
+          <t>2:01.57</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>134.70</t>
+          <t>121.57</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Нетания</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>25.11.2022</t>
+          <t>04.12.2015</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2022-11-25</t>
+          <t>2015-12-04</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>баттерфляй 200 м (бассейн 25 м)</t>
+          <t>брасс 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2019,33 +2019,33 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>*Чимрова Светлана</t>
+          <t>Чикунова Евгения</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2:03.76</t>
+          <t>2:14.70</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>123.76</t>
+          <t>134.70</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>30.09.2021</t>
+          <t>25.11.2022</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2022-11-25</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>вольный стиль 200 м (бассейн 25 м)</t>
+          <t>баттерфляй 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2067,33 +2067,33 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Попова Вероника</t>
+          <t>*Чимрова Светлана</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1:52.46</t>
+          <t>2:03.76</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>112.46</t>
+          <t>123.76</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Нетания</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>05.12.2015</t>
+          <t>30.09.2021</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2015-12-05</t>
+          <t>2021-09-30</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>комплексное плавание 200 м (бассейн 25 м)</t>
+          <t>вольный стиль 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2115,33 +2115,33 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ефимова Юлия</t>
+          <t>Попова Вероника</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2:06.79</t>
+          <t>1:52.46</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>126.79</t>
+          <t>112.46</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>Нетания</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>03.09.2016</t>
+          <t>05.12.2015</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2016-09-03</t>
+          <t>2015-12-05</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>вольный стиль 400 м (бассейн 25 м)</t>
+          <t>комплексное плавание 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2163,33 +2163,33 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Андрусенко Вероника</t>
+          <t>Ефимова Юлия</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>3:58.25</t>
+          <t>2:06.79</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>238.25</t>
+          <t>126.79</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>08.11.2019</t>
+          <t>03.09.2016</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2019-11-08</t>
+          <t>2016-09-03</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>комплексное плавание 400 м (бассейн 25 м)</t>
+          <t>вольный стиль 400 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2211,33 +2211,33 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Иваненко Анастасия</t>
+          <t>Андрусенко Вероника</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>4:31.13</t>
+          <t>3:58.25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>271.13</t>
+          <t>238.25</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Берлин</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>15.11.2009</t>
+          <t>08.11.2019</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2009-11-15</t>
+          <t>2019-11-08</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>вольный стиль 800 м (бассейн 25 м)</t>
+          <t>комплексное плавание 400 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2259,33 +2259,33 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Кирпичникова Анастасия</t>
+          <t>Иваненко Анастасия</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>8:04.65</t>
+          <t>4:31.13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>484.65</t>
+          <t>271.13</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Берлин</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>03.11.2021</t>
+          <t>15.11.2009</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2009-11-15</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>вольный стиль 1500 м (бассейн 25 м)</t>
+          <t>вольный стиль 800 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2313,12 +2313,12 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>15:18.30</t>
+          <t>8:04.65</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>918.30</t>
+          <t>484.65</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2328,12 +2328,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>05.11.2021</t>
+          <t>03.11.2021</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2021-11-05</t>
+          <t>2021-11-03</t>
         </is>
       </c>
     </row>
@@ -2345,32 +2345,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4 х 50 м вольный стиль (бассейн 25 м)</t>
+          <t>вольный стиль 1500 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>эстафета</t>
+          <t>личное</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Сборная России</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Насретдинова Розалия · Суркова Арина · Каменева Мария · Клепикова Дарья</t>
-        </is>
-      </c>
+          <t>Кирпичникова Анастасия</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1:34.92</t>
+          <t>15:18.30</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>94.92</t>
+          <t>918.30</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2380,12 +2376,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>02.11.2021</t>
+          <t>05.11.2021</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
+          <t>2021-11-05</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2393,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4 х 50 м комбинированная (бассейн 25 м)</t>
+          <t>4 х 50 м вольный стиль (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2412,17 +2408,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Каменева Мария · Годун Ника · Суркова Арина · Клепикова Дарья</t>
+          <t>Насретдинова Розалия · Суркова Арина · Каменева Мария · Клепикова Дарья</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1:44.19</t>
+          <t>1:34.92</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>104.19</t>
+          <t>94.92</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2432,12 +2428,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>04.11.2021</t>
+          <t>02.11.2021</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2021-11-04</t>
+          <t>2021-11-02</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2445,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4 х 100 м вольный стиль (бассейн 25 м)</t>
+          <t>4 х 50 м комбинированная (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2464,32 +2460,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Клепикова Дарья · Трофимова Дарья · Степанова Милана · Суркова Арина</t>
+          <t>Каменева Мария · Годун Ника · Суркова Арина · Клепикова Дарья</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>3:28.73</t>
+          <t>1:44.19</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>208.73</t>
+          <t>104.19</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10.12.2024</t>
+          <t>04.11.2021</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2021-11-04</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2497,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4 х 100 м комбинированная (бассейн 25 м)</t>
+          <t>4 х 100 м вольный стиль (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2516,17 +2512,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Агапитова Елизавета · Чикунова Евгения · Суркова Арина · Клепикова Дарья</t>
+          <t>Клепикова Дарья · Трофимова Дарья · Степанова Милана · Суркова Арина</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>3:49.35</t>
+          <t>3:28.73</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>229.35</t>
+          <t>208.73</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2536,12 +2532,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>15.12.2024</t>
+          <t>10.12.2024</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>2024-12-10</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2549,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4 х 200 м вольный стиль (бассейн 25 м)</t>
+          <t>4 х 100 м комбинированная (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2568,80 +2564,84 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Егорова Анна · Муллакаева Дарья · Гуженкова Анастасия · Андрусенко Вероника</t>
+          <t>Агапитова Елизавета · Чикунова Евгения · Суркова Арина · Клепикова Дарья</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>7:36.64</t>
+          <t>3:49.35</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>456.64</t>
+          <t>229.35</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Ханчжоу</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>15.12.2018</t>
+          <t>15.12.2024</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2018-12-15</t>
+          <t>2024-12-15</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Мужчины, бассейн 50 м</t>
+          <t>Женщины, бассейн 25 м</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>на спине 50 м</t>
+          <t>4 х 200 м вольный стиль (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>личное</t>
+          <t>эстафета</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Колесников Климент</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
+          <t>Сборная России</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Егорова Анна · Муллакаева Дарья · Гуженкова Анастасия · Андрусенко Вероника</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>7:36.64</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>456.64</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Ханчжоу</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>27.07.2023</t>
+          <t>15.12.2018</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>2018-12-15</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>брасс 50 м</t>
+          <t>на спине 50 м</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2663,18 +2663,18 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Кожакин Иван</t>
+          <t>Колесников Климент</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>17.04.2025</t>
+          <t>27.07.2023</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2023-07-27</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>баттерфляй 50 м</t>
+          <t>брасс 50 м</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2711,18 +2711,18 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Костин Олег</t>
+          <t>Кожакин Иван</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>22.62</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>22.62</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>19.04.2023</t>
+          <t>17.04.2025</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2025-04-17</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>вольный стиль 50 м</t>
+          <t>баттерфляй 50 м</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2759,33 +2759,33 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Морозов Владимир</t>
+          <t>Корнев Егор</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>21.27</t>
+          <t>22.59</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>21.27</t>
+          <t>22.59</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Сингапур</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>15.08.2019</t>
+          <t>10.06.2026</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2019-08-15</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>на спине 100 м</t>
+          <t>вольный стиль 50 м</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2807,18 +2807,18 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Колесников Климент</t>
+          <t>Корнев Егор</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>51.82</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>51.82</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>26.07.2023</t>
+          <t>09.06.2026</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>брасс 100 м</t>
+          <t>на спине 100 м</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2855,33 +2855,33 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Пригода Кирилл</t>
+          <t>Колесников Климент</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>51.82</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>51.82</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Сингапур</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>27.07.2025</t>
+          <t>26.07.2023</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2023-07-26</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>баттерфляй 100 м</t>
+          <t>брасс 100 м</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2903,33 +2903,33 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Шевляков Роман</t>
+          <t>Пригода Кирилл</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>50.70</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>50.70</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Сингапур</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>24.06.2025</t>
+          <t>27.07.2025</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-07-27</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>вольный стиль 100 м</t>
+          <t>баттерфляй 100 м</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2951,33 +2951,33 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Колесников Климент</t>
+          <t>Шевляков Роман</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>50.70</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>50.70</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Токио</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>28.07.2021</t>
+          <t>24.06.2025</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2025-06-24</t>
         </is>
       </c>
     </row>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>на спине 200 м</t>
+          <t>вольный стиль 100 м</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2999,18 +2999,18 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Рылов Евгений</t>
+          <t>Корнев Егор</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1:53.23</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>113.23</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>08.04.2021</t>
+          <t>11.06.2026</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>брасс 200 м</t>
+          <t>на спине 200 м</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3047,33 +3047,33 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Чупков Антон</t>
+          <t>Рылов Евгений</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2:06.12</t>
+          <t>1:53.23</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>126.12</t>
+          <t>113.23</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Кванджу</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>26.07.2019</t>
+          <t>08.04.2021</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2019-07-26</t>
+          <t>2021-04-08</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>баттерфляй 200 м</t>
+          <t>брасс 200 м</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3095,33 +3095,33 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Скворцов Николай</t>
+          <t>Чупков Антон</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1:54.31</t>
+          <t>2:06.12</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>114.31</t>
+          <t>126.12</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Пекин</t>
+          <t>Кванджу</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>12.08.2008</t>
+          <t>26.07.2019</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2008-08-12</t>
+          <t>2019-07-26</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>вольный стиль 200 м</t>
+          <t>баттерфляй 200 м</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3143,33 +3143,33 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Изотов Данила</t>
+          <t>Скворцов Николай</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1:43.90</t>
+          <t>1:54.31</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>103.90</t>
+          <t>114.31</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Рим</t>
+          <t>Пекин</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>28.07.2009</t>
+          <t>12.08.2008</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2009-07-28</t>
+          <t>2008-08-12</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>комплексное плавание 200 м</t>
+          <t>вольный стиль 200 м</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3191,33 +3191,33 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Бородин Илья</t>
+          <t>Изотов Данила</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1:56.75</t>
+          <t>1:43.90</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>116.75</t>
+          <t>103.90</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Екатеринбург</t>
+          <t>Рим</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>24.07.2024</t>
+          <t>28.07.2009</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2009-07-28</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>вольный стиль 400 м</t>
+          <t>комплексное плавание 200 м</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3239,33 +3239,33 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Лобинцев Никита</t>
+          <t>Бородин Илья</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>3:43.45</t>
+          <t>1:56.75</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>223.45</t>
+          <t>116.75</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Пекин</t>
+          <t>Екатеринбург</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>09.08.2008</t>
+          <t>24.07.2024</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2008-08-09</t>
+          <t>2024-07-24</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>комплексное плавание 400 м</t>
+          <t>вольный стиль 400 м</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3287,33 +3287,33 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Бородин Илья</t>
+          <t>Лобинцев Никита</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>4:08.05</t>
+          <t>3:43.45</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>248.05</t>
+          <t>223.45</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Пекин</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>25.07.2022</t>
+          <t>09.08.2008</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2008-08-09</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>вольный стиль 800 м</t>
+          <t>комплексное плавание 400 м</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3335,18 +3335,18 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Степанов Александр</t>
+          <t>Бородин Илья</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>7:42.47</t>
+          <t>4:08.05</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>462.47</t>
+          <t>248.05</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>18.04.2023</t>
+          <t>25.07.2022</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2022-07-25</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>вольный стиль 1500 м</t>
+          <t>вольный стиль 800 м</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3383,33 +3383,33 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Прилуков Юрий</t>
+          <t>Степанов Александр</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>14:41.13</t>
+          <t>7:42.47</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>881.13</t>
+          <t>462.47</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Пекин</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>15.08.2008</t>
+          <t>18.04.2023</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2008-08-15</t>
+          <t>2023-04-18</t>
         </is>
       </c>
     </row>
@@ -3421,47 +3421,43 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>4 х 100 м вольный стиль</t>
+          <t>вольный стиль 1500 м</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>эстафета</t>
+          <t>личное</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Сборная России</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Лагунов Евгений · Гречин Андрей · Изотов Данила · Сухоруков Александр</t>
-        </is>
-      </c>
+          <t>Прилуков Юрий</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>3:09.52</t>
+          <t>14:41.13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>189.52</t>
+          <t>881.13</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Рим</t>
+          <t>Пекин</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>26.07.2009</t>
+          <t>15.08.2008</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2009-07-26</t>
+          <t>2008-08-15</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3469,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>4 х 100 м комбинированная</t>
+          <t>4 х 100 м вольный стиль</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3488,32 +3484,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Лифинцев Мирон · Пригода Кирилл · Минаков Андрей · Корнев Егор</t>
+          <t>Лагунов Евгений · Гречин Андрей · Изотов Данила · Сухоруков Александр</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>3:26.93</t>
+          <t>3:09.52</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>206.93</t>
+          <t>189.52</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Сингапур</t>
+          <t>Рим</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>03.08.2025</t>
+          <t>26.07.2009</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2009-07-26</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3521,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4 х 200 м вольный стиль</t>
+          <t>4 х 100 м комбинированная</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3540,80 +3536,84 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Лобинцев Никита · Полищук Михаил · Изотов Данила · Сухоруков Александр</t>
+          <t>Лифинцев Мирон · Пригода Кирилл · Минаков Андрей · Корнев Егор</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>6:59.15</t>
+          <t>3:26.93</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>419.15</t>
+          <t>206.93</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Рим</t>
+          <t>Сингапур</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>31.07.2009</t>
+          <t>03.08.2025</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2009-07-31</t>
+          <t>2025-08-03</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Мужчины, бассейн 25 м</t>
+          <t>Мужчины, бассейн 50 м</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>на спине 50 м (бассейн 25 м)</t>
+          <t>4 х 200 м вольный стиль</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>личное</t>
+          <t>эстафета</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Колесников Климент</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
+          <t>Сборная России</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Лобинцев Никита · Полищук Михаил · Изотов Данила · Сухоруков Александр</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>22.11</t>
+          <t>6:59.15</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>22.11</t>
+          <t>419.15</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Рим</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>23.11.2022</t>
+          <t>31.07.2009</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2022-11-23</t>
+          <t>2009-07-31</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>брасс 50 м  (бассейн 25 м)</t>
+          <t>на спине 50 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3635,33 +3635,33 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Пригода Кирилл</t>
+          <t>Колесников Климент</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>22.11</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>22.11</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>14.12.2024</t>
+          <t>23.11.2022</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2024-12-14</t>
+          <t>2022-11-23</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>баттерфляй 50 м (бассейн 25 м)</t>
+          <t>брасс 50 м  (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3683,33 +3683,33 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Корнев Егор</t>
+          <t>Пригода Кирилл</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>25.48</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>25.48</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>07.11.2025</t>
+          <t>14.12.2024</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2024-12-14</t>
         </is>
       </c>
     </row>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>вольный стиль 50 м (бассейн 25 м)</t>
+          <t>баттерфляй 50 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3731,33 +3731,33 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Морозов Владимир</t>
+          <t>Корнев Егор</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Копенгаген</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>15.12.2017</t>
+          <t>07.11.2025</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2017-12-15</t>
+          <t>2025-11-07</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>на спине 100 м (бассейн 25 м)</t>
+          <t>вольный стиль 50 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3779,33 +3779,33 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>*Колесников Климент</t>
+          <t>Морозов Владимир</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>48.58</t>
+          <t>20.31</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>48.58</t>
+          <t>20.31</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Копенгаген</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>21.11.2020</t>
+          <t>15.12.2017</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2020-11-21</t>
+          <t>2017-12-15</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>брасс 100 м (бассейн 25 м)</t>
+          <t>на спине 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3827,18 +3827,18 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Пригода Кирилл</t>
+          <t>*Колесников Климент</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>55.49</t>
+          <t>48.58</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>55.49</t>
+          <t>48.58</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>12.12.2024</t>
+          <t>21.11.2020</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2020-11-21</t>
         </is>
       </c>
     </row>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>баттерфляй 100 м (бассейн 25 м)</t>
+          <t>брасс 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3875,33 +3875,33 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Коротышкин Евгений</t>
+          <t>Пригода Кирилл</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>48.48</t>
+          <t>55.49</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>48.48</t>
+          <t>55.49</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Берлин</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>15.11.2009</t>
+          <t>12.12.2024</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2009-11-15</t>
+          <t>2024-12-12</t>
         </is>
       </c>
     </row>
@@ -3913,7 +3913,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>вольный стиль 100 м (бассейн 25 м)</t>
+          <t>баттерфляй 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3923,33 +3923,33 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Морозов Владимир</t>
+          <t>Коротышкин Евгений</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>48.48</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>48.48</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Сингапур</t>
+          <t>Берлин</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>16.11.2018</t>
+          <t>15.11.2009</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2018-11-16</t>
+          <t>2009-11-15</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>комплексное плавание 100 м (бассейн 25 м)</t>
+          <t>вольный стиль 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3977,27 +3977,27 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>50.26</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>50.26</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Эйндховен</t>
+          <t>Сингапур</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>28.09.2018</t>
+          <t>16.11.2018</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2018-09-28</t>
+          <t>2018-11-16</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>на спине 200 м (бассейн 25 м)</t>
+          <t>комплексное плавание 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4019,33 +4019,33 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Вятчанин Аркадий</t>
+          <t>Морозов Владимир</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1:46.11</t>
+          <t>50.26</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>106.11</t>
+          <t>50.26</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Берлин</t>
+          <t>Эйндховен</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>15.11.2009</t>
+          <t>28.09.2018</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2009-11-15</t>
+          <t>2018-09-28</t>
         </is>
       </c>
     </row>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>брасс 200 м (бассейн 25 м)</t>
+          <t>на спине 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4067,33 +4067,33 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Пригода Кирилл</t>
+          <t>Вятчанин Аркадий</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2:00.16</t>
+          <t>1:46.11</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>120.16</t>
+          <t>106.11</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Ханчжоу</t>
+          <t>Берлин</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>13.12.2018</t>
+          <t>15.11.2009</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2018-12-13</t>
+          <t>2009-11-15</t>
         </is>
       </c>
     </row>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>баттерфляй 200 м (бассейн 25 м)</t>
+          <t>брасс 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4115,33 +4115,33 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Скворцов Николай</t>
+          <t>Пригода Кирилл</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1:49.46</t>
+          <t>2:00.16</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>109.46</t>
+          <t>120.16</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Стамбул</t>
+          <t>Ханчжоу</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>12.12.2009</t>
+          <t>13.12.2018</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2009-12-12</t>
+          <t>2018-12-13</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>вольный стиль 200 м (бассейн 25 м)</t>
+          <t>баттерфляй 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4163,18 +4163,18 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Изотов Данила</t>
+          <t>Скворцов Николай</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1:40.08</t>
+          <t>1:49.46</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>100.08</t>
+          <t>109.46</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>13.12.2009</t>
+          <t>12.12.2009</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2009-12-13</t>
+          <t>2009-12-12</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>комплексное плавание 200 м (бассейн 25 м)</t>
+          <t>вольный стиль 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4211,33 +4211,33 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Сударев Алексей</t>
+          <t>Изотов Данила</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1:52.13</t>
+          <t>1:40.08</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>112.13</t>
+          <t>100.08</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Санкт-Петербург</t>
+          <t>Стамбул</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>18.12.2023</t>
+          <t>13.12.2009</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2009-12-13</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>вольный стиль 400 м (бассейн 25 м)</t>
+          <t>комплексное плавание 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4259,33 +4259,33 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Красных Александр</t>
+          <t>Сударев Алексей</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>3:35.30</t>
+          <t>1:52.13</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>215.30</t>
+          <t>112.13</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Виндзор</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>06.12.2016</t>
+          <t>18.12.2023</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2016-12-06</t>
+          <t>2023-12-18</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>комплексное плавание 400 м (бассейн 25 м)</t>
+          <t>вольный стиль 400 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4307,33 +4307,33 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Бородин Илья</t>
+          <t>Красных Александр</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>3:56.47</t>
+          <t>3:35.30</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>236.47</t>
+          <t>215.30</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Абу Даби</t>
+          <t>Виндзор</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>20.12.2021</t>
+          <t>06.12.2016</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2021-12-20</t>
+          <t>2016-12-06</t>
         </is>
       </c>
     </row>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>вольный стиль 800 м (бассейн 25 м)</t>
+          <t>комплексное плавание 400 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4355,33 +4355,33 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Лузин Савелий</t>
+          <t>Бородин Илья</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>7:32.36</t>
+          <t>3:56.47</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>452.36</t>
+          <t>236.47</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Абу Даби</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>11.11.2025</t>
+          <t>20.12.2021</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2021-12-20</t>
         </is>
       </c>
     </row>
@@ -4393,7 +4393,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>вольный стиль 1500 м (бассейн 25 м)</t>
+          <t>вольный стиль 800 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4403,33 +4403,33 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Прилуков Юрий</t>
+          <t>Лузин Савелий</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>14:16.13</t>
+          <t>7:32.36</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>856.13</t>
+          <t>452.36</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Хельсинки</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>09.12.2006</t>
+          <t>11.11.2025</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2006-12-09</t>
+          <t>2025-11-11</t>
         </is>
       </c>
     </row>
@@ -4441,47 +4441,43 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>4 х 50 м вольный стиль (бассейн 25 м)</t>
+          <t>вольный стиль 1500 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>эстафета</t>
+          <t>личное</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Сборная России</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Морозов Владимир · Седов Евгений · Кузьменко Иван · Рылов Евгений</t>
-        </is>
-      </c>
+          <t>Прилуков Юрий</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1:22.22</t>
+          <t>14:16.13</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>82.22</t>
+          <t>856.13</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Ханчжоу</t>
+          <t>Хельсинки</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>14.12.2018</t>
+          <t>09.12.2006</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2018-12-14</t>
+          <t>2006-12-09</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4489,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>4 х 50 м комбинированная (бассейн 25 м)</t>
+          <t>4 х 50 м вольный стиль (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4508,32 +4504,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Колесников Климент · Пригода Кирилл · Попков Александр · Морозов Владимир</t>
+          <t>Морозов Владимир · Седов Евгений · Кузьменко Иван · Рылов Евгений</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1:30.44</t>
+          <t>1:22.22</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>90.44</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Копенгаген</t>
+          <t>Ханчжоу</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>17.12.2017</t>
+          <t>14.12.2018</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2017-12-17</t>
+          <t>2018-12-14</t>
         </is>
       </c>
     </row>
@@ -4545,7 +4541,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>4 х 100 м вольный стиль (бассейн 25 м)</t>
+          <t>4 х 50 м комбинированная (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4560,32 +4556,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Гринев Владислав · Фесиков Сергей · Морозов Владимир · Колесников Климент</t>
+          <t>Колесников Климент · Пригода Кирилл · Попков Александр · Морозов Владимир</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>3:03.11</t>
+          <t>1:30.44</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>183.11</t>
+          <t>90.44</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Ханчжоу</t>
+          <t>Копенгаген</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>11.12.2018</t>
+          <t>17.12.2017</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2018-12-11</t>
+          <t>2017-12-17</t>
         </is>
       </c>
     </row>
@@ -4597,7 +4593,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>4 х 100 м комбинированная (бассейн 25 м)</t>
+          <t>4 х 100 м вольный стиль (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4612,32 +4608,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Лифинцев Мирон · Пригода Кирилл · Минаков Андрей · Корнев Егор</t>
+          <t>Гринев Владислав · Фесиков Сергей · Морозов Владимир · Колесников Климент</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>3:18.68</t>
+          <t>3:03.11</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>198.68</t>
+          <t>183.11</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Ханчжоу</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>15.12.2024</t>
+          <t>11.12.2018</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>2018-12-11</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4645,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>4 х 200 м вольный стиль (бассейн 25 м)</t>
+          <t>4 х 100 м комбинированная (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4664,44 +4660,44 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Малютин Мартин · Вековищев Михаил · Гирев Иван · Красных Александр</t>
+          <t>Лифинцев Мирон · Пригода Кирилл · Минаков Андрей · Корнев Егор</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>6:46.84</t>
+          <t>3:18.68</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>406.84</t>
+          <t>198.68</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Ханчжоу</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>14.12.2018</t>
+          <t>15.12.2024</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2018-12-14</t>
+          <t>2024-12-15</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Смешанные эстафеты</t>
+          <t>Мужчины, бассейн 25 м</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>4 х 50 м вольный стиль (бассейн 25 м)</t>
+          <t>4 х 200 м вольный стиль (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4716,32 +4712,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Морозов Владимир · Гринев Владислав · Суркова Арина · Каменева Мария</t>
+          <t>Малютин Мартин · Вековищев Михаил · Гирев Иван · Красных Александр</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1:28.31</t>
+          <t>6:46.84</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>88.31</t>
+          <t>406.84</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Глазго</t>
+          <t>Ханчжоу</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>07.12.2019</t>
+          <t>14.12.2018</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2019-12-07</t>
+          <t>2018-12-14</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4749,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>4 х 50 м комбинированная (бассейн 25 м)</t>
+          <t>4 х 50 м вольный стиль (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4768,32 +4764,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Лифинцев Мирон · Пригода Кирилл · Суркова Арина · Трофимова Дарья</t>
+          <t>Морозов Владимир · Гринев Владислав · Суркова Арина · Каменева Мария</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1:35.36</t>
+          <t>1:28.31</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>95.36</t>
+          <t>88.31</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Глазго</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>11.12.2024</t>
+          <t>07.12.2019</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2019-12-07</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4801,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>4 х 100 м вольный стиль</t>
+          <t>4 х 50 м комбинированная (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4820,32 +4816,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Корнев Егор · Гирев Иван · Трофимова Дарья · Клепикова Дарья</t>
+          <t>Лифинцев Мирон · Пригода Кирилл · Суркова Арина · Трофимова Дарья</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>3:19.68</t>
+          <t>1:35.36</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>199.68</t>
+          <t>95.36</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Сингапур</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>02.08.2025</t>
+          <t>11.12.2024</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2024-12-11</t>
         </is>
       </c>
     </row>
@@ -4857,45 +4853,97 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
+          <t>4 х 100 м вольный стиль</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>эстафета</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Сборная России</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Корнев Егор · Гирев Иван · Трофимова Дарья · Клепикова Дарья</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>3:19.68</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>199.68</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Сингапур</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>02.08.2025</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Смешанные эстафеты</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
           <t>4 х 100 м комбинированная</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>эстафета</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>Сборная России</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>Лифинцев Мирон · Пригода Кирилл · Клепикова Дарья · Трофимова Дарья</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>3:37.97</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>217.97</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>Сингапур</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>30.07.2025</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>2025-07-30</t>
         </is>
@@ -4912,7 +4960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4963,7 +5011,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Фесикова Анастасия</t>
+          <t>Гайфутдинова Алина</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -4974,86 +5022,86 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Глазго</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>04.08.2018</t>
+          <t>19.04.2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>брасс 50 м</t>
+          <t>на спине 50 м</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ефимова Юлия</t>
+          <t>Фесикова Анастасия</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>27.23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Барселона</t>
+          <t>Глазго</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>04.08.2013</t>
+          <t>04.08.2018</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>баттерфляй 50 м</t>
+          <t>брасс 50 м</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Суркова Арина</t>
+          <t>Ефимова Юлия</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Барселона</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.04.2023</t>
+          <t>04.08.2013</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>вольный стиль 50 м</t>
+          <t>баттерфляй 50 м</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Каменева Мария</t>
+          <t>Суркова Арина</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24.20</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5063,98 +5111,98 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>09.04.2021</t>
+          <t>19.04.2023</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>на спине 100 м</t>
+          <t>вольный стиль 50 м</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Зуева Анастасия</t>
+          <t>Каменева Мария</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>58.18</t>
+          <t>24.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Рим</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>28.07.2009</t>
+          <t>09.04.2021</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>брасс 100 м</t>
+          <t>на спине 100 м</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ефимова Юлия</t>
+          <t>Зуева Анастасия</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1:04.36</t>
+          <t>58.18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Рим</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.07.2017</t>
+          <t>28.07.2009</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>баттерфляй 100 м</t>
+          <t>брасс 100 м</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Клепикова Дарья</t>
+          <t>Ефимова Юлия</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>56.42</t>
+          <t>1:04.36</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Сингапур</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>27.07.2025</t>
+          <t>24.07.2017</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>вольный стиль 100 м</t>
+          <t>баттерфляй 100 м</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5165,7 +5213,7 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52.98</t>
+          <t>56.42</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5175,238 +5223,238 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>01.08.2025</t>
+          <t>27.07.2025</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>на спине 200 м</t>
+          <t>вольный стиль 100 м</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Зуева Анастасия</t>
+          <t>Клепикова Дарья</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2:04.94</t>
+          <t>52.98</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Рим</t>
+          <t>Сингапур</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01.08.2009</t>
+          <t>01.08.2025</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>брасс 200 м</t>
+          <t>на спине 200 м</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Чикунова Евгения</t>
+          <t>Зуева Анастасия</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2:17.55</t>
+          <t>2:04.94</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Рим</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.04.2023</t>
+          <t>01.08.2009</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>баттерфляй 200 м</t>
+          <t>брасс 200 м</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Чимрова Светлана</t>
+          <t>Чикунова Евгения</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2:07.33</t>
+          <t>2:17.55</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Глазго</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06.08.2018</t>
+          <t>21.04.2023</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>вольный стиль 200 м</t>
+          <t>баттерфляй 200 м</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Попова Вероника</t>
+          <t>Чимрова Светлана</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1:55.08</t>
+          <t>2:07.33</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Глазго</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>25.07.2017</t>
+          <t>06.08.2018</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>комплексное плавание 200 м</t>
+          <t>вольный стиль 200 м</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Андреева Виктория</t>
+          <t>Попова Вероника</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2:09.56</t>
+          <t>1:55.08</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>19.04.2016</t>
+          <t>25.07.2017</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>вольный стиль 400 м</t>
+          <t>комплексное плавание 200 м</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Егорова Анна</t>
+          <t>Андреева Виктория</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4:04.10</t>
+          <t>2:09.56</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>04.04.2021</t>
+          <t>19.04.2016</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>комплексное плавание 400 м</t>
+          <t>вольный стиль 400 м</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Мартынова Яна</t>
+          <t>Егорова Анна</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4:36.25</t>
+          <t>4:04.10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Пекин</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>09.08.2008</t>
+          <t>04.04.2021</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>вольный стиль 800 м</t>
+          <t>комплексное плавание 400 м</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Кирпичникова Анастасия</t>
+          <t>Мартынова Яна</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8:18.77</t>
+          <t>4:36.25</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Токио</t>
+          <t>Пекин</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>29.07.2021</t>
+          <t>09.08.2008</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>вольный стиль 1500 м</t>
+          <t>вольный стиль 800 м</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5417,7 +5465,7 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15:50.22</t>
+          <t>8:18.77</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -5427,46 +5475,42 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>26.07.2021</t>
+          <t>29.07.2021</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4 х 100 м вольный стиль</t>
+          <t>вольный стиль 1500 м</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Сборная России</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Трофимова Дарья · Кузнецова Александра · Гайфутдинова Алина · Клепикова Дарья</t>
-        </is>
-      </c>
+          <t>Кирпичникова Анастасия</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3:34.69</t>
+          <t>15:50.22</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Сингапур</t>
+          <t>Токио</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>27.07.2025</t>
+          <t>26.07.2021</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4 х 100 м комбинированная</t>
+          <t>4 х 100 м вольный стиль</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5476,52 +5520,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Фесикова Анастасия · Ефимова Юлия · Чимрова Светлана · Попова Вероника</t>
+          <t>Трофимова Дарья · Кузнецова Александра · Гайфутдинова Алина · Клепикова Дарья</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3:53.38</t>
+          <t>3:34.69</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Сингапур</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>30.07.2017</t>
+          <t>27.07.2025</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>4 х 100 м комбинированная</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Сборная России</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Фесикова Анастасия · Ефимова Юлия · Чимрова Светлана · Попова Вероника</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>3:53.38</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Будапешт</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>30.07.2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>4 х 200 м вольный стиль</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Сборная России</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Егорова Анна · Гуженкова Анастасия · Саламатина Валерия · Андрусенко Вероника</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>7:48.25</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Кванджу</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>25.07.2019</t>
         </is>
@@ -6363,13 +6439,13 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Костин Олег</t>
+          <t>Корнев Егор</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>22.62</t>
+          <t>22.59</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -6379,7 +6455,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.04.2023</t>
+          <t>10.06.2026</t>
         </is>
       </c>
     </row>
@@ -6391,23 +6467,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Морозов Владимир</t>
+          <t>Корнев Егор</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21.27</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Сингапур</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>15.08.2019</t>
+          <t>09.06.2026</t>
         </is>
       </c>
     </row>
@@ -6503,23 +6579,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Колесников Климент</t>
+          <t>Корнев Егор</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Токио</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>28.07.2021</t>
+          <t>11.06.2026</t>
         </is>
       </c>
     </row>

--- a/public/records.xlsx
+++ b/public/records.xlsx
@@ -35,7 +35,7 @@
       <color rgb="00FAFAFA"/>
     </font>
     <font>
-      <name val="Menlo"/>
+      <name val="Consolas"/>
     </font>
   </fonts>
   <fills count="3">
@@ -68,7 +68,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -523,12 +525,12 @@
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>27.23</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>27.23</t>
         </is>
@@ -571,12 +573,12 @@
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>27.23</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>27.23</t>
         </is>
@@ -619,12 +621,12 @@
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>29.52</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>29.52</t>
         </is>
@@ -667,12 +669,12 @@
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>25.30</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>25.30</t>
         </is>
@@ -715,12 +717,12 @@
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>24.20</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>24.20</t>
         </is>
@@ -763,12 +765,12 @@
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>58.18</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>58.18</t>
         </is>
@@ -811,12 +813,12 @@
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1:04.36</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>64.36</t>
         </is>
@@ -859,12 +861,12 @@
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>56.42</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>56.42</t>
         </is>
@@ -907,12 +909,12 @@
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>52.98</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>52.98</t>
         </is>
@@ -955,12 +957,12 @@
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>2:04.94</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>124.94</t>
         </is>
@@ -1003,12 +1005,12 @@
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>2:17.55</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>137.55</t>
         </is>
@@ -1051,12 +1053,12 @@
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>2:07.33</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>127.33</t>
         </is>
@@ -1099,12 +1101,12 @@
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>1:55.08</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>115.08</t>
         </is>
@@ -1147,12 +1149,12 @@
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>2:09.56</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>129.56</t>
         </is>
@@ -1195,12 +1197,12 @@
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>4:04.10</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>244.10</t>
         </is>
@@ -1243,12 +1245,12 @@
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>4:36.25</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>276.25</t>
         </is>
@@ -1291,12 +1293,12 @@
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>8:18.77</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>498.77</t>
         </is>
@@ -1339,12 +1341,12 @@
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>15:50.22</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>950.22</t>
         </is>
@@ -1391,12 +1393,12 @@
           <t>Трофимова Дарья · Кузнецова Александра · Гайфутдинова Алина · Клепикова Дарья</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>3:34.69</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>214.69</t>
         </is>
@@ -1443,12 +1445,12 @@
           <t>Фесикова Анастасия · Ефимова Юлия · Чимрова Светлана · Попова Вероника</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>3:53.38</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>233.38</t>
         </is>
@@ -1495,12 +1497,12 @@
           <t>Егорова Анна · Гуженкова Анастасия · Саламатина Валерия · Андрусенко Вероника</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>7:48.25</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>468.25</t>
         </is>
@@ -1543,12 +1545,12 @@
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>25.60</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>25.60</t>
         </is>
@@ -1591,12 +1593,12 @@
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>29.08</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>29.08</t>
         </is>
@@ -1639,12 +1641,12 @@
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>24.58</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>24.58</t>
         </is>
@@ -1687,12 +1689,12 @@
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>23.34</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>23.34</t>
         </is>
@@ -1735,12 +1737,12 @@
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>55.83</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>55.83</t>
         </is>
@@ -1783,12 +1785,12 @@
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>1:02.91</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>62.91</t>
         </is>
@@ -1831,12 +1833,12 @@
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>55.63</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>55.63</t>
         </is>
@@ -1879,12 +1881,12 @@
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>51.62</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>51.62</t>
         </is>
@@ -1927,12 +1929,12 @@
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>57.59</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>57.59</t>
         </is>
@@ -1975,12 +1977,12 @@
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>2:01.57</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>121.57</t>
         </is>
@@ -2023,12 +2025,12 @@
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>2:14.70</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>134.70</t>
         </is>
@@ -2071,12 +2073,12 @@
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>2:03.76</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>123.76</t>
         </is>
@@ -2119,12 +2121,12 @@
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>1:52.46</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>112.46</t>
         </is>
@@ -2167,12 +2169,12 @@
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>2:06.79</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>126.79</t>
         </is>
@@ -2215,12 +2217,12 @@
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>3:58.25</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>238.25</t>
         </is>
@@ -2263,12 +2265,12 @@
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>4:31.13</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>271.13</t>
         </is>
@@ -2311,12 +2313,12 @@
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>8:04.65</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>484.65</t>
         </is>
@@ -2359,12 +2361,12 @@
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>15:18.30</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>918.30</t>
         </is>
@@ -2411,12 +2413,12 @@
           <t>Насретдинова Розалия · Суркова Арина · Каменева Мария · Клепикова Дарья</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>1:34.92</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>94.92</t>
         </is>
@@ -2463,12 +2465,12 @@
           <t>Каменева Мария · Годун Ника · Суркова Арина · Клепикова Дарья</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1:44.19</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>104.19</t>
         </is>
@@ -2515,12 +2517,12 @@
           <t>Клепикова Дарья · Трофимова Дарья · Степанова Милана · Суркова Арина</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>3:28.73</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>208.73</t>
         </is>
@@ -2567,12 +2569,12 @@
           <t>Агапитова Елизавета · Чикунова Евгения · Суркова Арина · Клепикова Дарья</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>3:49.35</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>229.35</t>
         </is>
@@ -2619,12 +2621,12 @@
           <t>Егорова Анна · Муллакаева Дарья · Гуженкова Анастасия · Андрусенко Вероника</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>7:36.64</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>456.64</t>
         </is>
@@ -2667,12 +2669,12 @@
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>23.55</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>23.55</t>
         </is>
@@ -2715,12 +2717,12 @@
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>26.46</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>26.46</t>
         </is>
@@ -2763,12 +2765,12 @@
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>22.59</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>22.59</t>
         </is>
@@ -2811,12 +2813,12 @@
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>21.06</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>21.06</t>
         </is>
@@ -2859,12 +2861,12 @@
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>51.82</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>51.82</t>
         </is>
@@ -2907,12 +2909,12 @@
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>58.53</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>58.53</t>
         </is>
@@ -2955,12 +2957,12 @@
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>50.70</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>50.70</t>
         </is>
@@ -3003,12 +3005,12 @@
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>46.96</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>46.96</t>
         </is>
@@ -3051,12 +3053,12 @@
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1:53.23</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>113.23</t>
         </is>
@@ -3099,12 +3101,12 @@
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>2:06.12</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>126.12</t>
         </is>
@@ -3147,12 +3149,12 @@
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1:54.31</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>114.31</t>
         </is>
@@ -3195,12 +3197,12 @@
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1:43.90</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>103.90</t>
         </is>
@@ -3243,12 +3245,12 @@
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1:56.75</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>116.75</t>
         </is>
@@ -3291,12 +3293,12 @@
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>3:43.45</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>223.45</t>
         </is>
@@ -3339,12 +3341,12 @@
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>4:08.05</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>248.05</t>
         </is>
@@ -3387,12 +3389,12 @@
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>7:42.47</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>462.47</t>
         </is>
@@ -3435,12 +3437,12 @@
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>14:41.13</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>881.13</t>
         </is>
@@ -3487,12 +3489,12 @@
           <t>Лагунов Евгений · Гречин Андрей · Изотов Данила · Сухоруков Александр</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>3:09.52</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>189.52</t>
         </is>
@@ -3539,12 +3541,12 @@
           <t>Лифинцев Мирон · Пригода Кирилл · Минаков Андрей · Корнев Егор</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>3:26.93</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>206.93</t>
         </is>
@@ -3591,12 +3593,12 @@
           <t>Лобинцев Никита · Полищук Михаил · Изотов Данила · Сухоруков Александр</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>6:59.15</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>419.15</t>
         </is>
@@ -3639,12 +3641,12 @@
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>22.11</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>22.11</t>
         </is>
@@ -3687,12 +3689,12 @@
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>25.48</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>25.48</t>
         </is>
@@ -3735,12 +3737,12 @@
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>21.73</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>21.73</t>
         </is>
@@ -3783,12 +3785,12 @@
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>20.31</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>20.31</t>
         </is>
@@ -3831,12 +3833,12 @@
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>48.58</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>48.58</t>
         </is>
@@ -3879,12 +3881,12 @@
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>55.49</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>55.49</t>
         </is>
@@ -3927,12 +3929,12 @@
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>48.48</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>48.48</t>
         </is>
@@ -3975,12 +3977,12 @@
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>44.95</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>44.95</t>
         </is>
@@ -4023,12 +4025,12 @@
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>50.26</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>50.26</t>
         </is>
@@ -4071,12 +4073,12 @@
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1:46.11</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>106.11</t>
         </is>
@@ -4119,12 +4121,12 @@
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>2:00.16</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>120.16</t>
         </is>
@@ -4167,12 +4169,12 @@
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1:49.46</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>109.46</t>
         </is>
@@ -4215,12 +4217,12 @@
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1:40.08</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>100.08</t>
         </is>
@@ -4263,12 +4265,12 @@
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1:52.13</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>112.13</t>
         </is>
@@ -4311,12 +4313,12 @@
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>3:35.30</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>215.30</t>
         </is>
@@ -4359,12 +4361,12 @@
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>3:56.47</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>236.47</t>
         </is>
@@ -4407,12 +4409,12 @@
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>7:32.36</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>452.36</t>
         </is>
@@ -4455,12 +4457,12 @@
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>14:16.13</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>856.13</t>
         </is>
@@ -4507,12 +4509,12 @@
           <t>Морозов Владимир · Седов Евгений · Кузьменко Иван · Рылов Евгений</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1:22.22</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>82.22</t>
         </is>
@@ -4559,12 +4561,12 @@
           <t>Колесников Климент · Пригода Кирилл · Попков Александр · Морозов Владимир</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1:30.44</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>90.44</t>
         </is>
@@ -4611,12 +4613,12 @@
           <t>Гринев Владислав · Фесиков Сергей · Морозов Владимир · Колесников Климент</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>3:03.11</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>183.11</t>
         </is>
@@ -4663,12 +4665,12 @@
           <t>Лифинцев Мирон · Пригода Кирилл · Минаков Андрей · Корнев Егор</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>3:18.68</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>198.68</t>
         </is>
@@ -4715,12 +4717,12 @@
           <t>Малютин Мартин · Вековищев Михаил · Гирев Иван · Красных Александр</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>6:46.84</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>406.84</t>
         </is>
@@ -4767,12 +4769,12 @@
           <t>Морозов Владимир · Гринев Владислав · Суркова Арина · Каменева Мария</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>1:28.31</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>88.31</t>
         </is>
@@ -4819,12 +4821,12 @@
           <t>Лифинцев Мирон · Пригода Кирилл · Суркова Арина · Трофимова Дарья</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1:35.36</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>95.36</t>
         </is>
@@ -4871,12 +4873,12 @@
           <t>Корнев Егор · Гирев Иван · Трофимова Дарья · Клепикова Дарья</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>3:19.68</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>199.68</t>
         </is>
@@ -4923,12 +4925,12 @@
           <t>Лифинцев Мирон · Пригода Кирилл · Клепикова Дарья · Трофимова Дарья</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>3:37.97</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>217.97</t>
         </is>

--- a/public/records.xlsx
+++ b/public/records.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Все" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Женщины, бассейн 50 м" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Женщины, бассейн 25 м" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Мужчины, бассейн 50 м" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Мужчины, бассейн 25 м" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Смешанные эстафеты" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Все" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Женщины, бассейн 50 м" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Женщины, бассейн 25 м" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мужчины, бассейн 50 м" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мужчины, бассейн 25 м" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Смешанные эстафеты" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/public/records.xlsx
+++ b/public/records.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Все" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Женщины, бассейн 50 м" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Женщины, бассейн 25 м" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мужчины, бассейн 50 м" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мужчины, бассейн 25 м" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Смешанные эстафеты" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Все" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Женщины, бассейн 50 м" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Женщины, бассейн 25 м" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Мужчины, бассейн 50 м" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Мужчины, бассейн 25 м" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Смешанные эстафеты" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/public/records.xlsx
+++ b/public/records.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -527,27 +527,27 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>27.23</t>
+          <t>26.91</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>27.23</t>
+          <t>26.91</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Санкт-Петербург</t>
+          <t>Париж</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>19.04.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>на спине 50 м</t>
+          <t>брасс 50 м</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -569,33 +569,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Фесикова Анастасия</t>
+          <t>Ефимова Юлия</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>27.23</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>27.23</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Глазго</t>
+          <t>Барселона</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>04.08.2018</t>
+          <t>04.08.2013</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2018-08-04</t>
+          <t>2013-08-04</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>брасс 50 м</t>
+          <t>баттерфляй 50 м</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -617,33 +617,33 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ефимова Юлия</t>
+          <t>Суркова Арина</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Барселона</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>04.08.2013</t>
+          <t>19.04.2023</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2013-08-04</t>
+          <t>2023-04-19</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>баттерфляй 50 м</t>
+          <t>вольный стиль 50 м</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -665,18 +665,18 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Суркова Арина</t>
+          <t>Каменева Мария</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>24.20</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>24.20</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -686,12 +686,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>19.04.2023</t>
+          <t>09.04.2021</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2021-04-09</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>вольный стиль 50 м</t>
+          <t>на спине 100 м</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -713,33 +713,33 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Каменева Мария</t>
+          <t>Зуева Анастасия</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24.20</t>
+          <t>58.18</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>24.20</t>
+          <t>58.18</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Рим</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>09.04.2021</t>
+          <t>28.07.2009</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2021-04-09</t>
+          <t>2009-07-28</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>на спине 100 м</t>
+          <t>брасс 100 м</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -761,33 +761,33 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Зуева Анастасия</t>
+          <t>Ефимова Юлия</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58.18</t>
+          <t>1:04.36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>58.18</t>
+          <t>64.36</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Рим</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>28.07.2009</t>
+          <t>24.07.2017</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2009-07-28</t>
+          <t>2017-07-24</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>брасс 100 м</t>
+          <t>баттерфляй 100 м</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -809,33 +809,33 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ефимова Юлия</t>
+          <t>Клепикова Дарья</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1:04.36</t>
+          <t>56.42</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>64.36</t>
+          <t>56.42</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Сингапур</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>24.07.2017</t>
+          <t>27.07.2025</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2017-07-24</t>
+          <t>2025-07-27</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>баттерфляй 100 м</t>
+          <t>вольный стиль 100 м</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -863,12 +863,12 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56.42</t>
+          <t>52.98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>56.42</t>
+          <t>52.98</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>27.07.2025</t>
+          <t>01.08.2025</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-08-01</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>вольный стиль 100 м</t>
+          <t>на спине 200 м</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -905,33 +905,33 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Клепикова Дарья</t>
+          <t>Зуева Анастасия</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52.98</t>
+          <t>2:04.94</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>52.98</t>
+          <t>124.94</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Сингапур</t>
+          <t>Рим</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>01.08.2025</t>
+          <t>01.08.2009</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2009-08-01</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>на спине 200 м</t>
+          <t>брасс 200 м</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -953,33 +953,33 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Зуева Анастасия</t>
+          <t>Чикунова Евгения</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2:04.94</t>
+          <t>2:17.55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>124.94</t>
+          <t>137.55</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Рим</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>01.08.2009</t>
+          <t>21.04.2023</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2023-04-21</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>брасс 200 м</t>
+          <t>баттерфляй 200 м</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1001,33 +1001,33 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Чикунова Евгения</t>
+          <t>Чимрова Светлана</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2:17.55</t>
+          <t>2:07.33</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>137.55</t>
+          <t>127.33</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Глазго</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>21.04.2023</t>
+          <t>06.08.2018</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2023-04-21</t>
+          <t>2018-08-06</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>баттерфляй 200 м</t>
+          <t>вольный стиль 200 м</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1049,33 +1049,33 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Чимрова Светлана</t>
+          <t>Попова Вероника</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2:07.33</t>
+          <t>1:55.08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>127.33</t>
+          <t>115.08</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Глазго</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>06.08.2018</t>
+          <t>25.07.2017</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2018-08-06</t>
+          <t>2017-07-25</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>вольный стиль 200 м</t>
+          <t>комплексное плавание 200 м</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1097,33 +1097,33 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Попова Вероника</t>
+          <t>Андреева Виктория</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1:55.08</t>
+          <t>2:09.56</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>115.08</t>
+          <t>129.56</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>25.07.2017</t>
+          <t>19.04.2016</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2017-07-25</t>
+          <t>2016-04-19</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>комплексное плавание 200 м</t>
+          <t>вольный стиль 400 м</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1145,33 +1145,33 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Андреева Виктория</t>
+          <t>Егорова Анна</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2:09.56</t>
+          <t>4:04.10</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>129.56</t>
+          <t>244.10</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>19.04.2016</t>
+          <t>04.04.2021</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2016-04-19</t>
+          <t>2021-04-04</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>вольный стиль 400 м</t>
+          <t>комплексное плавание 400 м</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1193,33 +1193,33 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Егорова Анна</t>
+          <t>Мартынова Яна</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4:04.10</t>
+          <t>4:36.25</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>244.10</t>
+          <t>276.25</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Пекин</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>04.04.2021</t>
+          <t>09.08.2008</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2021-04-04</t>
+          <t>2008-08-09</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>комплексное плавание 400 м</t>
+          <t>вольный стиль 800 м</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1241,33 +1241,33 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Мартынова Яна</t>
+          <t>Кирпичникова Анастасия</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4:36.25</t>
+          <t>8:18.77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>276.25</t>
+          <t>498.77</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Пекин</t>
+          <t>Токио</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>09.08.2008</t>
+          <t>29.07.2021</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2008-08-09</t>
+          <t>2021-07-29</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>вольный стиль 800 м</t>
+          <t>вольный стиль 1500 м</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1295,12 +1295,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8:18.77</t>
+          <t>15:50.22</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>498.77</t>
+          <t>950.22</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>29.07.2021</t>
+          <t>26.07.2021</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2021-07-29</t>
+          <t>2021-07-26</t>
         </is>
       </c>
     </row>
@@ -1327,43 +1327,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>вольный стиль 1500 м</t>
+          <t>4 х 100 м вольный стиль</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>личное</t>
+          <t>эстафета</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Кирпичникова Анастасия</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>Сборная России</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Клепикова Дарья · Кузнецова Александра · Гайфутдинова Алина · Манохина Кира</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15:50.22</t>
+          <t>3:33.69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>950.22</t>
+          <t>213.69</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Токио</t>
+          <t>Париж</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>26.07.2021</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2021-07-26</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1379,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4 х 100 м вольный стиль</t>
+          <t>4 х 100 м комбинированная</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1390,32 +1394,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Трофимова Дарья · Кузнецова Александра · Гайфутдинова Алина · Клепикова Дарья</t>
+          <t>Фесикова Анастасия · Ефимова Юлия · Чимрова Светлана · Попова Вероника</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3:34.69</t>
+          <t>3:53.38</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>214.69</t>
+          <t>233.38</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Сингапур</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>27.07.2025</t>
+          <t>30.07.2017</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2017-07-30</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1431,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4 х 100 м комбинированная</t>
+          <t>4 х 200 м вольный стиль</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1442,84 +1446,80 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Фесикова Анастасия · Ефимова Юлия · Чимрова Светлана · Попова Вероника</t>
+          <t>Егорова Анна · Гуженкова Анастасия · Саламатина Валерия · Андрусенко Вероника</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3:53.38</t>
+          <t>7:48.25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>233.38</t>
+          <t>468.25</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Кванджу</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30.07.2017</t>
+          <t>25.07.2019</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2017-07-30</t>
+          <t>2019-07-25</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Женщины, бассейн 50 м</t>
+          <t>Женщины, бассейн 25 м</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4 х 200 м вольный стиль</t>
+          <t>на спине 50 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>эстафета</t>
+          <t>личное</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Сборная России</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Егорова Анна · Гуженкова Анастасия · Саламатина Валерия · Андрусенко Вероника</t>
-        </is>
-      </c>
+          <t>Каменева Мария</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7:48.25</t>
+          <t>25.60</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>468.25</t>
+          <t>25.60</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Кванджу</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>25.07.2019</t>
+          <t>24.11.2022</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2019-07-25</t>
+          <t>2022-11-24</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>на спине 50 м (бассейн 25 м)</t>
+          <t>брасс 50 м  (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1541,33 +1541,33 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Каменева Мария</t>
+          <t>Ефимова Юлия</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25.60</t>
+          <t>29.08</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>25.60</t>
+          <t>29.08</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Берлин</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>24.11.2022</t>
+          <t>21.10.2013</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2022-11-24</t>
+          <t>2013-10-21</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>брасс 50 м  (бассейн 25 м)</t>
+          <t>баттерфляй 50 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1589,33 +1589,33 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ефимова Юлия</t>
+          <t>Суркова Арина</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>24.58</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>24.58</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Берлин</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>21.10.2013</t>
+          <t>22.11.2023</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2013-10-21</t>
+          <t>2023-11-22</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>баттерфляй 50 м (бассейн 25 м)</t>
+          <t>вольный стиль 50 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1637,18 +1637,18 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Суркова Арина</t>
+          <t>Каменева Мария</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24.58</t>
+          <t>23.34</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>24.58</t>
+          <t>23.34</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>22.11.2023</t>
+          <t>16.12.2022</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2023-11-22</t>
+          <t>2022-12-16</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>вольный стиль 50 м (бассейн 25 м)</t>
+          <t>на спине 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1691,12 +1691,12 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23.34</t>
+          <t>55.83</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>23.34</t>
+          <t>55.83</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>16.12.2022</t>
+          <t>18.12.2022</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2022-12-16</t>
+          <t>2022-12-18</t>
         </is>
       </c>
     </row>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>на спине 100 м (бассейн 25 м)</t>
+          <t>брасс 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1733,33 +1733,33 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Каменева Мария</t>
+          <t>Ефимова Юлия</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>55.83</t>
+          <t>1:02.91</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>55.83</t>
+          <t>62.91</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Санкт-Петербург</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>18.12.2022</t>
+          <t>03.09.2016</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2016-09-03</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>брасс 100 м (бассейн 25 м)</t>
+          <t>баттерфляй 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1781,33 +1781,33 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ефимова Юлия</t>
+          <t>Суркова Арина</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1:02.91</t>
+          <t>55.63</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>62.91</t>
+          <t>55.63</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>03.09.2016</t>
+          <t>25.11.2023</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2016-09-03</t>
+          <t>2023-11-25</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>баттерфляй 100 м (бассейн 25 м)</t>
+          <t>вольный стиль 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1829,33 +1829,33 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Суркова Арина</t>
+          <t>Клепикова Дарья</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>55.63</t>
+          <t>51.62</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>55.63</t>
+          <t>51.62</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Санкт-Петербург</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>25.11.2023</t>
+          <t>12.12.2024</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2024-12-12</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>вольный стиль 100 м (бассейн 25 м)</t>
+          <t>комплексное плавание 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1877,33 +1877,33 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Клепикова Дарья</t>
+          <t>Каменева Мария</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>51.62</t>
+          <t>57.59</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>51.62</t>
+          <t>57.59</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Глазго</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>12.12.2024</t>
+          <t>06.12.2019</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2019-12-06</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>комплексное плавание 100 м (бассейн 25 м)</t>
+          <t>на спине 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1925,33 +1925,33 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Каменева Мария</t>
+          <t>Устинова Дарья К.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>57.59</t>
+          <t>2:01.57</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>57.59</t>
+          <t>121.57</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Глазго</t>
+          <t>Нетания</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>06.12.2019</t>
+          <t>04.12.2015</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2019-12-06</t>
+          <t>2015-12-04</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>на спине 200 м (бассейн 25 м)</t>
+          <t>брасс 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1973,33 +1973,33 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Устинова Дарья К.</t>
+          <t>Чикунова Евгения</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2:01.57</t>
+          <t>2:14.70</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>121.57</t>
+          <t>134.70</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Нетания</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>04.12.2015</t>
+          <t>25.11.2022</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2015-12-04</t>
+          <t>2022-11-25</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>брасс 200 м (бассейн 25 м)</t>
+          <t>баттерфляй 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2021,33 +2021,33 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Чикунова Евгения</t>
+          <t>*Чимрова Светлана</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2:14.70</t>
+          <t>2:03.76</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>134.70</t>
+          <t>123.76</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>25.11.2022</t>
+          <t>30.09.2021</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2022-11-25</t>
+          <t>2021-09-30</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>баттерфляй 200 м (бассейн 25 м)</t>
+          <t>вольный стиль 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2069,33 +2069,33 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>*Чимрова Светлана</t>
+          <t>Попова Вероника</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2:03.76</t>
+          <t>1:52.46</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>123.76</t>
+          <t>112.46</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Нетания</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>30.09.2021</t>
+          <t>05.12.2015</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2015-12-05</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>вольный стиль 200 м (бассейн 25 м)</t>
+          <t>комплексное плавание 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2117,33 +2117,33 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Попова Вероника</t>
+          <t>Ефимова Юлия</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1:52.46</t>
+          <t>2:06.79</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>112.46</t>
+          <t>126.79</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Нетания</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>05.12.2015</t>
+          <t>03.09.2016</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2015-12-05</t>
+          <t>2016-09-03</t>
         </is>
       </c>
     </row>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>комплексное плавание 200 м (бассейн 25 м)</t>
+          <t>вольный стиль 400 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2165,33 +2165,33 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ефимова Юлия</t>
+          <t>Андрусенко Вероника</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2:06.79</t>
+          <t>3:58.25</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>126.79</t>
+          <t>238.25</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>03.09.2016</t>
+          <t>08.11.2019</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2016-09-03</t>
+          <t>2019-11-08</t>
         </is>
       </c>
     </row>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>вольный стиль 400 м (бассейн 25 м)</t>
+          <t>комплексное плавание 400 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2213,33 +2213,33 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Андрусенко Вероника</t>
+          <t>Иваненко Анастасия</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3:58.25</t>
+          <t>4:31.13</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>238.25</t>
+          <t>271.13</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Берлин</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>08.11.2019</t>
+          <t>15.11.2009</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2019-11-08</t>
+          <t>2009-11-15</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>комплексное плавание 400 м (бассейн 25 м)</t>
+          <t>вольный стиль 800 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2261,33 +2261,33 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Иваненко Анастасия</t>
+          <t>Кирпичникова Анастасия</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4:31.13</t>
+          <t>8:04.65</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>271.13</t>
+          <t>484.65</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Берлин</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>15.11.2009</t>
+          <t>03.11.2021</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2009-11-15</t>
+          <t>2021-11-03</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>вольный стиль 800 м (бассейн 25 м)</t>
+          <t>вольный стиль 1500 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2315,12 +2315,12 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>8:04.65</t>
+          <t>15:18.30</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>484.65</t>
+          <t>918.30</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>03.11.2021</t>
+          <t>05.11.2021</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2021-11-05</t>
         </is>
       </c>
     </row>
@@ -2347,28 +2347,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>вольный стиль 1500 м (бассейн 25 м)</t>
+          <t>4 х 50 м вольный стиль (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>личное</t>
+          <t>эстафета</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Кирпичникова Анастасия</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
+          <t>Сборная России</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Насретдинова Розалия · Суркова Арина · Каменева Мария · Клепикова Дарья</t>
+        </is>
+      </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>15:18.30</t>
+          <t>1:34.92</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>918.30</t>
+          <t>94.92</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2378,12 +2382,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>05.11.2021</t>
+          <t>02.11.2021</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2021-11-05</t>
+          <t>2021-11-02</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2399,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4 х 50 м вольный стиль (бассейн 25 м)</t>
+          <t>4 х 50 м комбинированная (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2410,17 +2414,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Насретдинова Розалия · Суркова Арина · Каменева Мария · Клепикова Дарья</t>
+          <t>Каменева Мария · Годун Ника · Суркова Арина · Клепикова Дарья</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1:34.92</t>
+          <t>1:44.19</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>94.92</t>
+          <t>104.19</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2430,12 +2434,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>02.11.2021</t>
+          <t>04.11.2021</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
+          <t>2021-11-04</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2451,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4 х 50 м комбинированная (бассейн 25 м)</t>
+          <t>4 х 100 м вольный стиль (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2462,32 +2466,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Каменева Мария · Годун Ника · Суркова Арина · Клепикова Дарья</t>
+          <t>Клепикова Дарья · Трофимова Дарья · Степанова Милана · Суркова Арина</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1:44.19</t>
+          <t>3:28.73</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>104.19</t>
+          <t>208.73</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>04.11.2021</t>
+          <t>10.12.2024</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2021-11-04</t>
+          <t>2024-12-10</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2503,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4 х 100 м вольный стиль (бассейн 25 м)</t>
+          <t>4 х 100 м комбинированная (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2514,17 +2518,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Клепикова Дарья · Трофимова Дарья · Степанова Милана · Суркова Арина</t>
+          <t>Агапитова Елизавета · Чикунова Евгения · Суркова Арина · Клепикова Дарья</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3:28.73</t>
+          <t>3:49.35</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>208.73</t>
+          <t>229.35</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2534,12 +2538,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10.12.2024</t>
+          <t>15.12.2024</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2024-12-15</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2555,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4 х 100 м комбинированная (бассейн 25 м)</t>
+          <t>4 х 200 м вольный стиль (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2566,84 +2570,80 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Агапитова Елизавета · Чикунова Евгения · Суркова Арина · Клепикова Дарья</t>
+          <t>Егорова Анна · Муллакаева Дарья · Гуженкова Анастасия · Андрусенко Вероника</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3:49.35</t>
+          <t>7:36.64</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>229.35</t>
+          <t>456.64</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Ханчжоу</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>15.12.2024</t>
+          <t>15.12.2018</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>2018-12-15</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Женщины, бассейн 25 м</t>
+          <t>Мужчины, бассейн 50 м</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4 х 200 м вольный стиль (бассейн 25 м)</t>
+          <t>на спине 50 м</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>эстафета</t>
+          <t>личное</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Сборная России</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Егорова Анна · Муллакаева Дарья · Гуженкова Анастасия · Андрусенко Вероника</t>
-        </is>
-      </c>
+          <t>Колесников Климент</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>7:36.64</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>456.64</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Ханчжоу</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>15.12.2018</t>
+          <t>27.07.2023</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2018-12-15</t>
+          <t>2023-07-27</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>на спине 50 м</t>
+          <t>брасс 50 м</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2665,18 +2665,18 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Колесников Климент</t>
+          <t>Кожакин Иван</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2686,12 +2686,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>27.07.2023</t>
+          <t>17.04.2025</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>2025-04-17</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>брасс 50 м</t>
+          <t>баттерфляй 50 м</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2713,33 +2713,33 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Кожакин Иван</t>
+          <t>Корнев Егор</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Париж</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>17.04.2025</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>баттерфляй 50 м</t>
+          <t>вольный стиль 50 м</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2767,12 +2767,12 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>22.59</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>22.59</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2782,12 +2782,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10.06.2026</t>
+          <t>09.06.2026</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>вольный стиль 50 м</t>
+          <t>на спине 100 м</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2809,18 +2809,18 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Корнев Егор</t>
+          <t>Колесников Климент</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>51.82</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>51.82</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>09.06.2026</t>
+          <t>26.07.2023</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2023-07-26</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>на спине 100 м</t>
+          <t>брасс 100 м</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2857,33 +2857,33 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Колесников Климент</t>
+          <t>Пригода Кирилл</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>51.82</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>51.82</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Сингапур</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>26.07.2023</t>
+          <t>27.07.2025</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2025-07-27</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>брасс 100 м</t>
+          <t>баттерфляй 100 м</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2905,33 +2905,33 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Пригода Кирилл</t>
+          <t>Шевляков Роман</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>50.70</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>50.70</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Сингапур</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>27.07.2025</t>
+          <t>24.06.2025</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-24</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>баттерфляй 100 м</t>
+          <t>вольный стиль 100 м</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2953,33 +2953,33 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Шевляков Роман</t>
+          <t>Корнев Егор</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>50.70</t>
+          <t>46.74</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>50.70</t>
+          <t>46.74</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Париж</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>24.06.2025</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>вольный стиль 100 м</t>
+          <t>на спине 200 м</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3001,18 +3001,18 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Корнев Егор</t>
+          <t>Рылов Евгений</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>1:53.23</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>113.23</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>11.06.2026</t>
+          <t>08.04.2021</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2021-04-08</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>на спине 200 м</t>
+          <t>брасс 200 м</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3049,33 +3049,33 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Рылов Евгений</t>
+          <t>Чупков Антон</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>1:53.23</t>
+          <t>2:06.12</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>113.23</t>
+          <t>126.12</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Кванджу</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>08.04.2021</t>
+          <t>26.07.2019</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2019-07-26</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>брасс 200 м</t>
+          <t>баттерфляй 200 м</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3097,33 +3097,33 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Чупков Антон</t>
+          <t>Скворцов Николай</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2:06.12</t>
+          <t>1:54.31</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>126.12</t>
+          <t>114.31</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Кванджу</t>
+          <t>Пекин</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>26.07.2019</t>
+          <t>12.08.2008</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2019-07-26</t>
+          <t>2008-08-12</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>баттерфляй 200 м</t>
+          <t>вольный стиль 200 м</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3145,33 +3145,33 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Скворцов Николай</t>
+          <t>Изотов Данила</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1:54.31</t>
+          <t>1:43.90</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>114.31</t>
+          <t>103.90</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Пекин</t>
+          <t>Рим</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>12.08.2008</t>
+          <t>28.07.2009</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2008-08-12</t>
+          <t>2009-07-28</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>вольный стиль 200 м</t>
+          <t>комплексное плавание 200 м</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3193,33 +3193,33 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Изотов Данила</t>
+          <t>Щербаков Михаил</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>1:43.90</t>
+          <t>1:56.16</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>103.90</t>
+          <t>116.16</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Рим</t>
+          <t>Париж</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>28.07.2009</t>
+          <t>16.08.2026</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2009-07-28</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>комплексное плавание 200 м</t>
+          <t>вольный стиль 400 м</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3241,33 +3241,33 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Бородин Илья</t>
+          <t>Лобинцев Никита</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>1:56.75</t>
+          <t>3:43.45</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>116.75</t>
+          <t>223.45</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Екатеринбург</t>
+          <t>Пекин</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>24.07.2024</t>
+          <t>09.08.2008</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2008-08-09</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>вольный стиль 400 м</t>
+          <t>комплексное плавание 400 м</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3289,33 +3289,33 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Лобинцев Никита</t>
+          <t>Бородин Илья</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>3:43.45</t>
+          <t>4:08.05</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>223.45</t>
+          <t>248.05</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Пекин</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>09.08.2008</t>
+          <t>25.07.2022</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2008-08-09</t>
+          <t>2022-07-25</t>
         </is>
       </c>
     </row>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>комплексное плавание 400 м</t>
+          <t>вольный стиль 800 м</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3337,18 +3337,18 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Бородин Илья</t>
+          <t>Степанов Александр</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>4:08.05</t>
+          <t>7:42.47</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>248.05</t>
+          <t>462.47</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>25.07.2022</t>
+          <t>18.04.2023</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2023-04-18</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>вольный стиль 800 м</t>
+          <t>вольный стиль 1500 м</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3385,33 +3385,33 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Степанов Александр</t>
+          <t>Прилуков Юрий</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>7:42.47</t>
+          <t>14:41.13</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>462.47</t>
+          <t>881.13</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Пекин</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>18.04.2023</t>
+          <t>15.08.2008</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2008-08-15</t>
         </is>
       </c>
     </row>
@@ -3423,43 +3423,47 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>вольный стиль 1500 м</t>
+          <t>4 х 100 м вольный стиль</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>личное</t>
+          <t>эстафета</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Прилуков Юрий</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
+          <t>Сборная России</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Лагунов Евгений · Гречин Андрей · Изотов Данила · Сухоруков Александр</t>
+        </is>
+      </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>14:41.13</t>
+          <t>3:09.52</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>881.13</t>
+          <t>189.52</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Пекин</t>
+          <t>Рим</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>15.08.2008</t>
+          <t>26.07.2009</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2008-08-15</t>
+          <t>2009-07-26</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3475,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>4 х 100 м вольный стиль</t>
+          <t>4 х 100 м комбинированная</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3486,32 +3490,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Лагунов Евгений · Гречин Андрей · Изотов Данила · Сухоруков Александр</t>
+          <t>Лифинцев Мирон · Пригода Кирилл · Минаков Андрей · Корнев Егор</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>3:09.52</t>
+          <t>3:26.93</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>189.52</t>
+          <t>206.93</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Рим</t>
+          <t>Сингапур</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>26.07.2009</t>
+          <t>03.08.2025</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2009-07-26</t>
+          <t>2025-08-03</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3527,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4 х 100 м комбинированная</t>
+          <t>4 х 200 м вольный стиль</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3538,84 +3542,80 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Лифинцев Мирон · Пригода Кирилл · Минаков Андрей · Корнев Егор</t>
+          <t>Лобинцев Никита · Полищук Михаил · Изотов Данила · Сухоруков Александр</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>3:26.93</t>
+          <t>6:59.15</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>206.93</t>
+          <t>419.15</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Сингапур</t>
+          <t>Рим</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>03.08.2025</t>
+          <t>31.07.2009</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2009-07-31</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Мужчины, бассейн 50 м</t>
+          <t>Мужчины, бассейн 25 м</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>4 х 200 м вольный стиль</t>
+          <t>на спине 50 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>эстафета</t>
+          <t>личное</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Сборная России</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Лобинцев Никита · Полищук Михаил · Изотов Данила · Сухоруков Александр</t>
-        </is>
-      </c>
+          <t>Колесников Климент</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>6:59.15</t>
+          <t>22.11</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>419.15</t>
+          <t>22.11</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Рим</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>31.07.2009</t>
+          <t>23.11.2022</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2009-07-31</t>
+          <t>2022-11-23</t>
         </is>
       </c>
     </row>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>на спине 50 м (бассейн 25 м)</t>
+          <t>брасс 50 м  (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3637,33 +3637,33 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Колесников Климент</t>
+          <t>Пригода Кирилл</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>22.11</t>
+          <t>25.48</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>22.11</t>
+          <t>25.48</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>23.11.2022</t>
+          <t>14.12.2024</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2022-11-23</t>
+          <t>2024-12-14</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>брасс 50 м  (бассейн 25 м)</t>
+          <t>баттерфляй 50 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3685,33 +3685,33 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Пригода Кирилл</t>
+          <t>Корнев Егор</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>14.12.2024</t>
+          <t>07.11.2025</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2024-12-14</t>
+          <t>2025-11-07</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>баттерфляй 50 м (бассейн 25 м)</t>
+          <t>вольный стиль 50 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3733,33 +3733,33 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Корнев Егор</t>
+          <t>Морозов Владимир</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>20.31</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>20.31</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Копенгаген</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>07.11.2025</t>
+          <t>15.12.2017</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2017-12-15</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>вольный стиль 50 м (бассейн 25 м)</t>
+          <t>на спине 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3781,33 +3781,33 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Морозов Владимир</t>
+          <t>*Колесников Климент</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>48.58</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>48.58</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Копенгаген</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>15.12.2017</t>
+          <t>21.11.2020</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2017-12-15</t>
+          <t>2020-11-21</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>на спине 100 м (бассейн 25 м)</t>
+          <t>брасс 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3829,18 +3829,18 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>*Колесников Климент</t>
+          <t>Пригода Кирилл</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>48.58</t>
+          <t>55.49</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>48.58</t>
+          <t>55.49</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>21.11.2020</t>
+          <t>12.12.2024</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2020-11-21</t>
+          <t>2024-12-12</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>брасс 100 м (бассейн 25 м)</t>
+          <t>баттерфляй 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3877,33 +3877,33 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Пригода Кирилл</t>
+          <t>Коротышкин Евгений</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>55.49</t>
+          <t>48.48</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>55.49</t>
+          <t>48.48</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Берлин</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>12.12.2024</t>
+          <t>15.11.2009</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2009-11-15</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>баттерфляй 100 м (бассейн 25 м)</t>
+          <t>вольный стиль 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3925,33 +3925,33 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Коротышкин Евгений</t>
+          <t>Морозов Владимир</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>48.48</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>48.48</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Берлин</t>
+          <t>Сингапур</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>15.11.2009</t>
+          <t>16.11.2018</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2009-11-15</t>
+          <t>2018-11-16</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>вольный стиль 100 м (бассейн 25 м)</t>
+          <t>комплексное плавание 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3979,27 +3979,27 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>50.26</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>50.26</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Сингапур</t>
+          <t>Эйндховен</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>16.11.2018</t>
+          <t>28.09.2018</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2018-11-16</t>
+          <t>2018-09-28</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>комплексное плавание 100 м (бассейн 25 м)</t>
+          <t>на спине 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4021,33 +4021,33 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Морозов Владимир</t>
+          <t>Вятчанин Аркадий</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>50.26</t>
+          <t>1:46.11</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>50.26</t>
+          <t>106.11</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Эйндховен</t>
+          <t>Берлин</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>28.09.2018</t>
+          <t>15.11.2009</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2018-09-28</t>
+          <t>2009-11-15</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>на спине 200 м (бассейн 25 м)</t>
+          <t>брасс 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4069,33 +4069,33 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Вятчанин Аркадий</t>
+          <t>Пригода Кирилл</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>1:46.11</t>
+          <t>2:00.16</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>106.11</t>
+          <t>120.16</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Берлин</t>
+          <t>Ханчжоу</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>15.11.2009</t>
+          <t>13.12.2018</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2009-11-15</t>
+          <t>2018-12-13</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>брасс 200 м (бассейн 25 м)</t>
+          <t>баттерфляй 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4117,33 +4117,33 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Пригода Кирилл</t>
+          <t>Скворцов Николай</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2:00.16</t>
+          <t>1:49.46</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>120.16</t>
+          <t>109.46</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Ханчжоу</t>
+          <t>Стамбул</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>13.12.2018</t>
+          <t>12.12.2009</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2018-12-13</t>
+          <t>2009-12-12</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>баттерфляй 200 м (бассейн 25 м)</t>
+          <t>вольный стиль 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4165,18 +4165,18 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Скворцов Николай</t>
+          <t>Изотов Данила</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>1:49.46</t>
+          <t>1:40.08</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>109.46</t>
+          <t>100.08</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>12.12.2009</t>
+          <t>13.12.2009</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2009-12-12</t>
+          <t>2009-12-13</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>вольный стиль 200 м (бассейн 25 м)</t>
+          <t>комплексное плавание 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4213,33 +4213,33 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Изотов Данила</t>
+          <t>Сударев Алексей</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>1:40.08</t>
+          <t>1:52.13</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>100.08</t>
+          <t>112.13</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Стамбул</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>13.12.2009</t>
+          <t>18.12.2023</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2009-12-13</t>
+          <t>2023-12-18</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>комплексное плавание 200 м (бассейн 25 м)</t>
+          <t>вольный стиль 400 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4261,33 +4261,33 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Сударев Алексей</t>
+          <t>Красных Александр</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>1:52.13</t>
+          <t>3:35.30</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>112.13</t>
+          <t>215.30</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Санкт-Петербург</t>
+          <t>Виндзор</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>18.12.2023</t>
+          <t>06.12.2016</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2016-12-06</t>
         </is>
       </c>
     </row>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>вольный стиль 400 м (бассейн 25 м)</t>
+          <t>комплексное плавание 400 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4309,33 +4309,33 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Красных Александр</t>
+          <t>Бородин Илья</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>3:35.30</t>
+          <t>3:56.47</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>215.30</t>
+          <t>236.47</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Виндзор</t>
+          <t>Абу Даби</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>06.12.2016</t>
+          <t>20.12.2021</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2016-12-06</t>
+          <t>2021-12-20</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>комплексное плавание 400 м (бассейн 25 м)</t>
+          <t>вольный стиль 800 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4357,33 +4357,33 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Бородин Илья</t>
+          <t>Лузин Савелий</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>3:56.47</t>
+          <t>7:32.36</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>236.47</t>
+          <t>452.36</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Абу Даби</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>20.12.2021</t>
+          <t>11.11.2025</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2021-12-20</t>
+          <t>2025-11-11</t>
         </is>
       </c>
     </row>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>вольный стиль 800 м (бассейн 25 м)</t>
+          <t>вольный стиль 1500 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4405,33 +4405,33 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Лузин Савелий</t>
+          <t>Прилуков Юрий</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>7:32.36</t>
+          <t>14:16.13</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>452.36</t>
+          <t>856.13</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Хельсинки</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>11.11.2025</t>
+          <t>09.12.2006</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2006-12-09</t>
         </is>
       </c>
     </row>
@@ -4443,43 +4443,47 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>вольный стиль 1500 м (бассейн 25 м)</t>
+          <t>4 х 50 м вольный стиль (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>личное</t>
+          <t>эстафета</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Прилуков Юрий</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
+          <t>Сборная России</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Морозов Владимир · Седов Евгений · Кузьменко Иван · Рылов Евгений</t>
+        </is>
+      </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>14:16.13</t>
+          <t>1:22.22</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>856.13</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Хельсинки</t>
+          <t>Ханчжоу</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>09.12.2006</t>
+          <t>14.12.2018</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2006-12-09</t>
+          <t>2018-12-14</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4495,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>4 х 50 м вольный стиль (бассейн 25 м)</t>
+          <t>4 х 50 м комбинированная (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4506,32 +4510,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Морозов Владимир · Седов Евгений · Кузьменко Иван · Рылов Евгений</t>
+          <t>Колесников Климент · Пригода Кирилл · Попков Александр · Морозов Владимир</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>1:22.22</t>
+          <t>1:30.44</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>82.22</t>
+          <t>90.44</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Ханчжоу</t>
+          <t>Копенгаген</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>14.12.2018</t>
+          <t>17.12.2017</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2018-12-14</t>
+          <t>2017-12-17</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4547,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>4 х 50 м комбинированная (бассейн 25 м)</t>
+          <t>4 х 100 м вольный стиль (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4558,32 +4562,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Колесников Климент · Пригода Кирилл · Попков Александр · Морозов Владимир</t>
+          <t>Гринев Владислав · Фесиков Сергей · Морозов Владимир · Колесников Климент</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>1:30.44</t>
+          <t>3:03.11</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>90.44</t>
+          <t>183.11</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Копенгаген</t>
+          <t>Ханчжоу</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>17.12.2017</t>
+          <t>11.12.2018</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2017-12-17</t>
+          <t>2018-12-11</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4599,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>4 х 100 м вольный стиль (бассейн 25 м)</t>
+          <t>4 х 100 м комбинированная (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4610,32 +4614,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Гринев Владислав · Фесиков Сергей · Морозов Владимир · Колесников Климент</t>
+          <t>Лифинцев Мирон · Пригода Кирилл · Минаков Андрей · Корнев Егор</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>3:03.11</t>
+          <t>3:18.68</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>183.11</t>
+          <t>198.68</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Ханчжоу</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>11.12.2018</t>
+          <t>15.12.2024</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2018-12-11</t>
+          <t>2024-12-15</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4651,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>4 х 100 м комбинированная (бассейн 25 м)</t>
+          <t>4 х 200 м вольный стиль (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4662,44 +4666,44 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Лифинцев Мирон · Пригода Кирилл · Минаков Андрей · Корнев Егор</t>
+          <t>Малютин Мартин · Вековищев Михаил · Гирев Иван · Красных Александр</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>3:18.68</t>
+          <t>6:46.84</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>198.68</t>
+          <t>406.84</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Ханчжоу</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>15.12.2024</t>
+          <t>14.12.2018</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>2018-12-14</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Мужчины, бассейн 25 м</t>
+          <t>Смешанные эстафеты</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>4 х 200 м вольный стиль (бассейн 25 м)</t>
+          <t>4 х 50 м вольный стиль (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4714,32 +4718,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Малютин Мартин · Вековищев Михаил · Гирев Иван · Красных Александр</t>
+          <t>Морозов Владимир · Гринев Владислав · Суркова Арина · Каменева Мария</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>6:46.84</t>
+          <t>1:28.31</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>406.84</t>
+          <t>88.31</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Ханчжоу</t>
+          <t>Глазго</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>14.12.2018</t>
+          <t>07.12.2019</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2018-12-14</t>
+          <t>2019-12-07</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4755,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>4 х 50 м вольный стиль (бассейн 25 м)</t>
+          <t>4 х 50 м комбинированная (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4766,32 +4770,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Морозов Владимир · Гринев Владислав · Суркова Арина · Каменева Мария</t>
+          <t>Лифинцев Мирон · Пригода Кирилл · Суркова Арина · Трофимова Дарья</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>1:28.31</t>
+          <t>1:35.36</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>88.31</t>
+          <t>95.36</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Глазго</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>07.12.2019</t>
+          <t>11.12.2024</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2019-12-07</t>
+          <t>2024-12-11</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4807,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>4 х 50 м комбинированная (бассейн 25 м)</t>
+          <t>4 х 100 м вольный стиль</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4818,32 +4822,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Лифинцев Мирон · Пригода Кирилл · Суркова Арина · Трофимова Дарья</t>
+          <t>Корнев Егор · Гирев Иван · Трофимова Дарья · Клепикова Дарья</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>1:35.36</t>
+          <t>3:19.68</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>95.36</t>
+          <t>199.68</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Сингапур</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>11.12.2024</t>
+          <t>02.08.2025</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-08-02</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4859,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>4 х 100 м вольный стиль</t>
+          <t>4 х 100 м комбинированная</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4870,17 +4874,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Корнев Егор · Гирев Иван · Трофимова Дарья · Клепикова Дарья</t>
+          <t>Лифинцев Мирон · Пригода Кирилл · Клепикова Дарья · Трофимова Дарья</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>3:19.68</t>
+          <t>3:37.97</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>199.68</t>
+          <t>217.97</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4890,62 +4894,10 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>02.08.2025</t>
+          <t>30.07.2025</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
-        <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Смешанные эстафеты</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>4 х 100 м комбинированная</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>эстафета</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Сборная России</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Лифинцев Мирон · Пригода Кирилл · Клепикова Дарья · Трофимова Дарья</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>3:37.97</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>217.97</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Сингапур</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>30.07.2025</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
         <is>
           <t>2025-07-30</t>
         </is>
@@ -4962,7 +4914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5019,91 +4971,91 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>27.23</t>
+          <t>26.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Санкт-Петербург</t>
+          <t>Париж</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19.04.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>на спине 50 м</t>
+          <t>брасс 50 м</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Фесикова Анастасия</t>
+          <t>Ефимова Юлия</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>27.23</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Глазго</t>
+          <t>Барселона</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>04.08.2018</t>
+          <t>04.08.2013</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>брасс 50 м</t>
+          <t>баттерфляй 50 м</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ефимова Юлия</t>
+          <t>Суркова Арина</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Барселона</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>04.08.2013</t>
+          <t>19.04.2023</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>баттерфляй 50 м</t>
+          <t>вольный стиль 50 м</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Суркова Арина</t>
+          <t>Каменева Мария</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>24.20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5113,98 +5065,98 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19.04.2023</t>
+          <t>09.04.2021</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>вольный стиль 50 м</t>
+          <t>на спине 100 м</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Каменева Мария</t>
+          <t>Зуева Анастасия</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24.20</t>
+          <t>58.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Рим</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>09.04.2021</t>
+          <t>28.07.2009</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>на спине 100 м</t>
+          <t>брасс 100 м</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Зуева Анастасия</t>
+          <t>Ефимова Юлия</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>58.18</t>
+          <t>1:04.36</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Рим</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>28.07.2009</t>
+          <t>24.07.2017</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>брасс 100 м</t>
+          <t>баттерфляй 100 м</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ефимова Юлия</t>
+          <t>Клепикова Дарья</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1:04.36</t>
+          <t>56.42</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Сингапур</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24.07.2017</t>
+          <t>27.07.2025</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>баттерфляй 100 м</t>
+          <t>вольный стиль 100 м</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5215,7 +5167,7 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>56.42</t>
+          <t>52.98</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5225,238 +5177,238 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>27.07.2025</t>
+          <t>01.08.2025</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>вольный стиль 100 м</t>
+          <t>на спине 200 м</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Клепикова Дарья</t>
+          <t>Зуева Анастасия</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>52.98</t>
+          <t>2:04.94</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Сингапур</t>
+          <t>Рим</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01.08.2025</t>
+          <t>01.08.2009</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>на спине 200 м</t>
+          <t>брасс 200 м</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Зуева Анастасия</t>
+          <t>Чикунова Евгения</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2:04.94</t>
+          <t>2:17.55</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Рим</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>01.08.2009</t>
+          <t>21.04.2023</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>брасс 200 м</t>
+          <t>баттерфляй 200 м</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Чикунова Евгения</t>
+          <t>Чимрова Светлана</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2:17.55</t>
+          <t>2:07.33</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Глазго</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.04.2023</t>
+          <t>06.08.2018</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>баттерфляй 200 м</t>
+          <t>вольный стиль 200 м</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Чимрова Светлана</t>
+          <t>Попова Вероника</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2:07.33</t>
+          <t>1:55.08</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Глазго</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06.08.2018</t>
+          <t>25.07.2017</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>вольный стиль 200 м</t>
+          <t>комплексное плавание 200 м</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Попова Вероника</t>
+          <t>Андреева Виктория</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1:55.08</t>
+          <t>2:09.56</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>25.07.2017</t>
+          <t>19.04.2016</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>комплексное плавание 200 м</t>
+          <t>вольный стиль 400 м</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Андреева Виктория</t>
+          <t>Егорова Анна</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2:09.56</t>
+          <t>4:04.10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>19.04.2016</t>
+          <t>04.04.2021</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>вольный стиль 400 м</t>
+          <t>комплексное плавание 400 м</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Егорова Анна</t>
+          <t>Мартынова Яна</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4:04.10</t>
+          <t>4:36.25</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Пекин</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>04.04.2021</t>
+          <t>09.08.2008</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>комплексное плавание 400 м</t>
+          <t>вольный стиль 800 м</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Мартынова Яна</t>
+          <t>Кирпичникова Анастасия</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4:36.25</t>
+          <t>8:18.77</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Пекин</t>
+          <t>Токио</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>09.08.2008</t>
+          <t>29.07.2021</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>вольный стиль 800 м</t>
+          <t>вольный стиль 1500 м</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5467,7 +5419,7 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8:18.77</t>
+          <t>15:50.22</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -5477,42 +5429,46 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>29.07.2021</t>
+          <t>26.07.2021</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>вольный стиль 1500 м</t>
+          <t>4 х 100 м вольный стиль</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Кирпичникова Анастасия</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>Сборная России</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Клепикова Дарья · Кузнецова Александра · Гайфутдинова Алина · Манохина Кира</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15:50.22</t>
+          <t>3:33.69</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Токио</t>
+          <t>Париж</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>26.07.2021</t>
+          <t>12.08.2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4 х 100 м вольный стиль</t>
+          <t>4 х 100 м комбинированная</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5522,29 +5478,29 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Трофимова Дарья · Кузнецова Александра · Гайфутдинова Алина · Клепикова Дарья</t>
+          <t>Фесикова Анастасия · Ефимова Юлия · Чимрова Светлана · Попова Вероника</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3:34.69</t>
+          <t>3:53.38</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Сингапур</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>27.07.2025</t>
+          <t>30.07.2017</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4 х 100 м комбинированная</t>
+          <t>4 х 200 м вольный стиль</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5554,52 +5510,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Фесикова Анастасия · Ефимова Юлия · Чимрова Светлана · Попова Вероника</t>
+          <t>Егорова Анна · Гуженкова Анастасия · Саламатина Валерия · Андрусенко Вероника</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3:53.38</t>
+          <t>7:48.25</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Кванджу</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
-        <is>
-          <t>30.07.2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>4 х 200 м вольный стиль</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Сборная России</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Егорова Анна · Гуженкова Анастасия · Саламатина Валерия · Андрусенко Вероника</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>7:48.25</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Кванджу</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
         <is>
           <t>25.07.2019</t>
         </is>
@@ -6447,17 +6371,17 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>22.59</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Париж</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10.06.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
     </row>
@@ -6587,17 +6511,17 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>46.74</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Париж</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>11.06.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
     </row>
@@ -6721,23 +6645,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Бородин Илья</t>
+          <t>Щербаков Михаил</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1:56.75</t>
+          <t>1:56.16</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Екатеринбург</t>
+          <t>Париж</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>24.07.2024</t>
+          <t>16.08.2026</t>
         </is>
       </c>
     </row>
